--- a/output3.xlsx
+++ b/output3.xlsx
@@ -419,22 +419,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Lower Limit</t>
+          <t>Lower Limit in mi/h</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Upper Limit</t>
+          <t>Upper Limit in mi/h</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Observed Vehicles(n)</t>
+          <t>Middle Speed (S) in mi/h</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Middle Speed (S)</t>
+          <t>Observed Vehicles(n)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -466,10 +466,10 @@
         <v>32</v>
       </c>
       <c r="C2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -492,10 +492,10 @@
         <v>34</v>
       </c>
       <c r="C3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3" t="n">
         <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>33</v>
       </c>
       <c r="E3" t="n">
         <v>1.358695652173913</v>
@@ -518,10 +518,10 @@
         <v>36</v>
       </c>
       <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>35</v>
       </c>
       <c r="E4" t="n">
         <v>1.358695652173913</v>
@@ -544,10 +544,10 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
+        <v>37</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>37</v>
       </c>
       <c r="E5" t="n">
         <v>1.902173913043478</v>
@@ -570,10 +570,10 @@
         <v>40</v>
       </c>
       <c r="C6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D6" t="n">
         <v>13</v>
-      </c>
-      <c r="D6" t="n">
-        <v>39</v>
       </c>
       <c r="E6" t="n">
         <v>3.532608695652174</v>
@@ -596,10 +596,10 @@
         <v>42</v>
       </c>
       <c r="C7" t="n">
+        <v>41</v>
+      </c>
+      <c r="D7" t="n">
         <v>21</v>
-      </c>
-      <c r="D7" t="n">
-        <v>41</v>
       </c>
       <c r="E7" t="n">
         <v>5.706521739130435</v>
@@ -622,10 +622,10 @@
         <v>44</v>
       </c>
       <c r="C8" t="n">
+        <v>43</v>
+      </c>
+      <c r="D8" t="n">
         <v>33</v>
-      </c>
-      <c r="D8" t="n">
-        <v>43</v>
       </c>
       <c r="E8" t="n">
         <v>8.967391304347826</v>
@@ -648,10 +648,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" t="n">
         <v>46</v>
-      </c>
-      <c r="D9" t="n">
-        <v>45</v>
       </c>
       <c r="E9" t="n">
         <v>12.5</v>
@@ -674,10 +674,10 @@
         <v>48</v>
       </c>
       <c r="C10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D10" t="n">
         <v>65</v>
-      </c>
-      <c r="D10" t="n">
-        <v>47</v>
       </c>
       <c r="E10" t="n">
         <v>17.66304347826087</v>
@@ -700,10 +700,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
+        <v>49</v>
+      </c>
+      <c r="D11" t="n">
         <v>40</v>
-      </c>
-      <c r="D11" t="n">
-        <v>49</v>
       </c>
       <c r="E11" t="n">
         <v>10.8695652173913</v>
@@ -726,10 +726,10 @@
         <v>52</v>
       </c>
       <c r="C12" t="n">
+        <v>51</v>
+      </c>
+      <c r="D12" t="n">
         <v>38</v>
-      </c>
-      <c r="D12" t="n">
-        <v>51</v>
       </c>
       <c r="E12" t="n">
         <v>10.32608695652174</v>
@@ -752,10 +752,10 @@
         <v>54</v>
       </c>
       <c r="C13" t="n">
+        <v>53</v>
+      </c>
+      <c r="D13" t="n">
         <v>30</v>
-      </c>
-      <c r="D13" t="n">
-        <v>53</v>
       </c>
       <c r="E13" t="n">
         <v>8.152173913043478</v>
@@ -778,10 +778,10 @@
         <v>56</v>
       </c>
       <c r="C14" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" t="n">
         <v>25</v>
-      </c>
-      <c r="D14" t="n">
-        <v>55</v>
       </c>
       <c r="E14" t="n">
         <v>6.793478260869565</v>
@@ -804,10 +804,10 @@
         <v>58</v>
       </c>
       <c r="C15" t="n">
+        <v>57</v>
+      </c>
+      <c r="D15" t="n">
         <v>18</v>
-      </c>
-      <c r="D15" t="n">
-        <v>57</v>
       </c>
       <c r="E15" t="n">
         <v>4.891304347826087</v>
@@ -830,10 +830,10 @@
         <v>60</v>
       </c>
       <c r="C16" t="n">
+        <v>59</v>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
-      </c>
-      <c r="D16" t="n">
-        <v>59</v>
       </c>
       <c r="E16" t="n">
         <v>2.717391304347826</v>
@@ -856,10 +856,10 @@
         <v>62</v>
       </c>
       <c r="C17" t="n">
+        <v>61</v>
+      </c>
+      <c r="D17" t="n">
         <v>7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>61</v>
       </c>
       <c r="E17" t="n">
         <v>1.902173913043478</v>
@@ -882,10 +882,10 @@
         <v>64</v>
       </c>
       <c r="C18" t="n">
+        <v>63</v>
+      </c>
+      <c r="D18" t="n">
         <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>63</v>
       </c>
       <c r="E18" t="n">
         <v>0.8152173913043478</v>
@@ -908,10 +908,10 @@
         <v>66</v>
       </c>
       <c r="C19" t="n">
+        <v>65</v>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>65</v>
       </c>
       <c r="E19" t="n">
         <v>0.5434782608695652</v>
@@ -934,10 +934,10 @@
         <v>68</v>
       </c>
       <c r="C20" t="n">
+        <v>67</v>
+      </c>
+      <c r="D20" t="n">
         <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>67</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
